--- a/data/cammy/output/cammy_gto.xlsx
+++ b/data/cammy/output/cammy_gto.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cammy OKI HSA FD MS (+11)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cammy OKI HSA FD Corner (+11)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cammy OKI HSA FD MS (+11)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -484,6 +485,253 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cammy OKI HSA FD Corner (+11)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Cammy1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Cammy2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Payoff</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>472.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Cammy OKI Heavy Spiral Arrow Forward Dash Corner (+11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>distribution</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>strategy_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Cammy1</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>cr.HP</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>0.11734264051029</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Cammy1</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>shimmy</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>0.2744012516548321</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Cammy1</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>throw</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>0.3936188406990517</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Cammy1</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>db</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>0.2146372671358261</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Cammy2</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>db</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>0.435000355837808</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>-472</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Cammy2</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>delayed tech</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>0.09554524598825474</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>-472</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Cammy2</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>reversal DP</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>0.1857585139318886</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>-472</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Cammy2</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>cr.MK</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>0.2836958842420487</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>-472</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/data/cammy/output/cammy_gto.xlsx
+++ b/data/cammy/output/cammy_gto.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cammy OKI HSA FD Corner (+11)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cammy OKI HSA FD MS (+11)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cammy Corner Throw (+17)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cammy OKI HSA FD Corner (+11)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cammy OKI HSA FD MS (+11)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -485,6 +486,145 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cammy Corner Throw (+17)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Cammy1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Cammy2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Payoff</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Cammy Corner Throw Loop (+17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>distribution</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>strategy_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Cammy1</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>throw</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Cammy2</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>n.j</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -726,7 +866,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/data/cammy/output/cammy_gto.xlsx
+++ b/data/cammy/output/cammy_gto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dfa238\pyproj\gambit_tekken8\data\cammy\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF32C148-ECBB-48C1-A675-777DA344AEF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC0D3D3-BF00-4DB4-A2FA-63657F04E0CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="1125" windowWidth="28365" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="405" yWindow="1230" windowWidth="28365" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cammy Corner Throw (+17)" sheetId="1" r:id="rId1"/>
@@ -96,10 +96,10 @@
     <t>Cammy OKI HSA FD MS (+11)</t>
   </si>
   <si>
-    <t>Cammy OKI Heavy Spiral Arrow Forward Dash Mid Screen (+11) (yellow = scramble)</t>
-  </si>
-  <si>
     <t>b.j</t>
+  </si>
+  <si>
+    <t>Cammy OKI Heavy Spiral Arrow Forward Dash Mid Screen (+11)</t>
   </si>
 </sst>
 </file>
@@ -224,7 +224,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -241,34 +241,28 @@
     <xf numFmtId="9" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="2" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="2" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -583,26 +577,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="10" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="11" t="s">
         <v>4</v>
       </c>
     </row>
@@ -637,86 +631,86 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="10" t="s">
+      <c r="A9" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="9">
         <v>0.25208969085843169</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="6">
         <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="10" t="s">
+      <c r="A10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="9">
         <v>0.29872628366724158</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="6">
         <v>303</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="10" t="s">
+      <c r="A11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="9">
         <v>0.44918402547432668</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="6">
         <v>303</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="11" t="s">
+      <c r="A12" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="8">
         <v>0.64290452813737942</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="7">
         <v>-303</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="11" t="s">
+      <c r="A13" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="8">
         <v>0.1137246725677136</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="7">
         <v>-303</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="11" t="s">
+      <c r="A14" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="8">
         <v>0.24337079929490699</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="7">
         <v>-303</v>
       </c>
     </row>
@@ -740,12 +734,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -800,7 +794,7 @@
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="9">
         <v>0.11734264051029</v>
       </c>
       <c r="D9" s="6">
@@ -814,7 +808,7 @@
       <c r="B10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="9">
         <v>0.27440125165483209</v>
       </c>
       <c r="D10" s="6">
@@ -828,7 +822,7 @@
       <c r="B11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="9">
         <v>0.39361884069905168</v>
       </c>
       <c r="D11" s="6">
@@ -842,7 +836,7 @@
       <c r="B12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="9">
         <v>0.21463726713582609</v>
       </c>
       <c r="D12" s="6">
@@ -850,58 +844,58 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="6" t="s">
+      <c r="A13" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="8">
         <v>0.43500035583780799</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="7">
         <v>-472</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="6" t="s">
+      <c r="A14" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="8">
         <v>9.5545245988254743E-2</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="7">
         <v>-472</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="6" t="s">
+      <c r="A15" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="8">
         <v>0.18575851393188861</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="7">
         <v>-472</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="6" t="s">
+      <c r="A16" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="8">
         <v>0.28369588424204872</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="7">
         <v>-472</v>
       </c>
     </row>
@@ -919,18 +913,18 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="80" customWidth="1"/>
+    <col min="2" max="2" width="54.140625" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -956,12 +950,12 @@
         <v>390.9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -985,7 +979,7 @@
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="9">
         <v>0.16997506234413959</v>
       </c>
       <c r="D9" s="6">
@@ -999,7 +993,7 @@
       <c r="B10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="9">
         <v>0.31903011701515438</v>
       </c>
       <c r="D10" s="6">
@@ -1013,7 +1007,7 @@
       <c r="B11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="9">
         <v>0.32578553615960099</v>
       </c>
       <c r="D11" s="6">
@@ -1027,7 +1021,7 @@
       <c r="B12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="9">
         <v>0.18520928448110491</v>
       </c>
       <c r="D12" s="6">
@@ -1035,44 +1029,44 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="6" t="s">
+      <c r="A13" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="8">
         <v>0.56668329177057353</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="7">
         <v>-391</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="7">
+      <c r="A14" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="8">
         <v>0.29566084788029923</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="7">
         <v>-391</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="6" t="s">
+      <c r="A15" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="8">
         <v>0.13765586034912719</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="7">
         <v>-391</v>
       </c>
     </row>

--- a/data/cammy/output/cammy_gto.xlsx
+++ b/data/cammy/output/cammy_gto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cammy Corner Throw (+17)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cammy OKI HSA FD Corner (+11)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cammy OKI HSA FD MS (+11)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cammy OKI throw MS (+17)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cammy Corner Throw (+17)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Cammy OKI HSA FD Corner (+11)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Cammy OKI HSA FD MS (+11)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cammy OKI throw MS (+17)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +37,9 @@
       <sz val="18"/>
     </font>
     <font>
+      <color rgb="007F6000"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00333333"/>
       <sz val="12"/>
@@ -50,20 +53,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
-    <font>
-      <color rgb="00006100"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <color rgb="FF9C0006"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <color rgb="007F6000"/>
-      <sz val="12"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -72,26 +63,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004F81BD"/>
-        <bgColor rgb="004F81BD"/>
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="004F81BD"/>
+        <bgColor rgb="004F81BD"/>
       </patternFill>
     </fill>
   </fills>
@@ -116,37 +95,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -518,7 +491,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
@@ -551,7 +524,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Cammy2</t>
         </is>
@@ -563,7 +536,7 @@
           <t>Payoff</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="5" t="n">
         <v>302.5</v>
       </c>
     </row>
@@ -573,7 +546,7 @@
           <t>Comment</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Cammy Corner Throw Loop (+17)</t>
         </is>
@@ -582,132 +555,132 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>distribution</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>strategy_value</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Cammy1</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Cammy1</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>throw</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="9" t="n">
         <v>0.2520896908584317</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="8" t="n">
         <v>303</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Cammy1</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Cammy1</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>mw s.MP</t>
         </is>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="9" t="n">
         <v>0.2987262836672416</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="8" t="n">
         <v>303</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Cammy1</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Cammy1</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>shimmy</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="9" t="n">
         <v>0.4491840254743267</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="8" t="n">
         <v>303</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Cammy2</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>db</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="9" t="n">
         <v>0.6429045281373794</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="8" t="n">
         <v>-303</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Cammy2</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>reversal DP</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="9" t="n">
         <v>0.1137246725677136</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="8" t="n">
         <v>-303</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Cammy2</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>backdash</t>
         </is>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="9" t="n">
         <v>0.243370799294907</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="8" t="n">
         <v>-303</v>
       </c>
     </row>
@@ -729,7 +702,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
@@ -762,7 +735,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Cammy2</t>
         </is>
@@ -774,7 +747,7 @@
           <t>Payoff</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="5" t="n">
         <v>521.6</v>
       </c>
     </row>
@@ -784,7 +757,7 @@
           <t>Comment</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Cammy OKI Heavy Spiral Arrow Forward Dash Corner (+11)</t>
         </is>
@@ -793,168 +766,168 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>distribution</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>strategy_value</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Cammy1</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Cammy1</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>cr.HP</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="9" t="n">
         <v>0.11734264051029</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="8" t="n">
         <v>522</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Cammy1</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Cammy1</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>shimmy</t>
         </is>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="9" t="n">
         <v>0.2744012516548321</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="8" t="n">
         <v>522</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Cammy1</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Cammy1</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>throw</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="9" t="n">
         <v>0.4346324712977949</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="8" t="n">
         <v>522</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Cammy1</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Cammy1</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>db</t>
         </is>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="9" t="n">
         <v>0.1736236365370829</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="8" t="n">
         <v>522</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Cammy2</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>db</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="9" t="n">
         <v>0.4270346334373293</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="8" t="n">
         <v>-522</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Cammy2</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>delayed tech</t>
         </is>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="9" t="n">
         <v>0.09379562234769004</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="8" t="n">
         <v>-522</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Cammy2</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>reversal DP</t>
         </is>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="9" t="n">
         <v>0.2006688963210702</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="8" t="n">
         <v>-522</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Cammy2</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>cr.MK</t>
         </is>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="9" t="n">
         <v>0.2785008478939104</v>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D16" s="8" t="n">
         <v>-522</v>
       </c>
     </row>
@@ -976,7 +949,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
@@ -1009,7 +982,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Cammy2</t>
         </is>
@@ -1021,7 +994,7 @@
           <t>Payoff</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="5" t="n">
         <v>390.9</v>
       </c>
     </row>
@@ -1031,7 +1004,7 @@
           <t>Comment</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Cammy OKI Heavy Spiral Arrow Forward Dash Mid Screen (+11) (yellow = scramble)</t>
         </is>
@@ -1040,150 +1013,150 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>distribution</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>strategy_value</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Cammy1</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Cammy1</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>cr.HP</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="9" t="n">
         <v>0.1699750623441396</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="8" t="n">
         <v>391</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Cammy1</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Cammy1</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>shimmy</t>
         </is>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="9" t="n">
         <v>0.3190301170151544</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="8" t="n">
         <v>391</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Cammy1</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Cammy1</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>throw</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="9" t="n">
         <v>0.325785536159601</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="8" t="n">
         <v>391</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Cammy1</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Cammy1</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>db</t>
         </is>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="9" t="n">
         <v>0.1852092844811049</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="8" t="n">
         <v>391</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Cammy2</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>db</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="9" t="n">
         <v>0.5666832917705735</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="8" t="n">
         <v>-391</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Cammy2</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>b.j</t>
         </is>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="9" t="n">
         <v>0.2956608478802992</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="8" t="n">
         <v>-391</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Cammy2</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>reversal DP</t>
         </is>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="9" t="n">
         <v>0.1376558603491272</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="8" t="n">
         <v>-391</v>
       </c>
     </row>
@@ -1201,12 +1174,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="104" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1238,7 +1211,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Cammy2NoDP</t>
         </is>
@@ -1250,8 +1223,8 @@
           <t>Payoff</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
-        <v>0</v>
+      <c r="B4" s="5" t="n">
+        <v>358.3</v>
       </c>
     </row>
     <row r="5">
@@ -1260,7 +1233,7 @@
           <t>Comment</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Cammy OKI throw MS (+17), with DRIVE REVERSAL WAKEUP since drive rush is reactable and can't be baited</t>
         </is>
@@ -1269,79 +1242,133 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>distribution</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>strategy_value</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Cammy1</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Cammy1</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>dr. mp</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n">
-        <v>0.6026587887740029</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>0</v>
+      <c r="C9" s="9" t="n">
+        <v>0.4968199608610567</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>358</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Cammy1</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Cammy1</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>dr. throw</t>
         </is>
       </c>
-      <c r="C10" s="10" t="n">
-        <v>0.397341211225997</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>0</v>
+      <c r="C10" s="9" t="n">
+        <v>0.3604452054794521</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>358</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Cammy1</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>dr. whiff jab</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>0.1427348336594912</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Cammy2NoDP</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>jab</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>0.4833403495198653</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>-358</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Cammy2NoDP</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>delayed tech</t>
         </is>
       </c>
-      <c r="C11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>0</v>
+      <c r="C13" s="9" t="n">
+        <v>0.02118224639330087</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>-358</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Cammy2NoDP</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>parry</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>0.4954774040868338</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>-358</v>
       </c>
     </row>
   </sheetData>
